--- a/data/trans_orig/Q5414-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2007</t>
+          <t>Población según si es capaz de comer solo en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>12232</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15400</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8385</t>
+          <t>8414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23882</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>356907</t>
+          <t>356639</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>368632</t>
+          <t>368675</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>567859</t>
+          <t>567851</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>582010</t>
+          <t>582220</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>930965</t>
+          <t>931153</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>948405</t>
+          <t>948621</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>83871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55108</t>
+          <t>54942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141928</t>
+          <t>141898</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149496</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6360</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16900</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26306</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>484502</t>
+          <t>484991</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>497122</t>
+          <t>496990</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,49 +2342,49 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>663783</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>655807</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>669677</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>96,89%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>98,94%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>663783</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>655489</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>670437</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1160</t>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1145491</t>
+          <t>1145012</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1164476</t>
+          <t>1164796</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2012</t>
+          <t>Población según si es capaz de comer solo en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17961</t>
+          <t>18210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8168</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>24398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>29369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43042</t>
+          <t>43075</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>388089</t>
+          <t>387505</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>405780</t>
+          <t>405877</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>593965</t>
+          <t>592960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>615832</t>
+          <t>615749</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>988769</t>
+          <t>990761</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1016642</t>
+          <t>1018280</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10127</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109301</t>
+          <t>108609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117611</t>
+          <t>117657</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73612</t>
+          <t>73950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82050</t>
+          <t>82118</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186848</t>
+          <t>186664</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198662</t>
+          <t>198594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3813,97 +3813,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21143</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10910</t>
+          <t>10554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28087</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>24990</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12823</t>
+          <t>12335</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31964</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>24262</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50422</t>
+          <t>51686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>527334</t>
+          <t>528178</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>547274</t>
+          <t>547452</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>693194</t>
+          <t>694725</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>717239</t>
+          <t>718013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1228646</t>
+          <t>1229937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1260258</t>
+          <t>1259874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2016</t>
+          <t>Población según si es capaz de comer solo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30682</t>
+          <t>30332</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>39270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>338793</t>
+          <t>338934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>349592</t>
+          <t>349680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>513926</t>
+          <t>512513</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>538071</t>
+          <t>536816</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>858470</t>
+          <t>859087</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>883704</t>
+          <t>884225</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4807</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>912</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4998</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -5412,97 +5412,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6982</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>1981</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>7105</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6767</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5982</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187668</t>
+          <t>187412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>180969</t>
+          <t>181092</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372997</t>
+          <t>372799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>379703</t>
+          <t>379700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5755,97 +5755,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5868,97 +5868,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6964</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>4709</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34404</t>
+          <t>34111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42958</t>
+          <t>42314</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>572371</t>
+          <t>571686</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>583215</t>
+          <t>583523</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>730820</t>
+          <t>732058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>756223</t>
+          <t>756715</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1309407</t>
+          <t>1310710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1336245</t>
+          <t>1336587</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de comer solo en 2023</t>
+          <t>Población según si es capaz de comer solo en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8567</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25634</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30559</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>258335</t>
+          <t>258665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265450</t>
+          <t>265695</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>467174</t>
+          <t>466979</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>481674</t>
+          <t>481848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>729597</t>
+          <t>729487</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>746050</t>
+          <t>745287</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3198</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1761</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>11747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>263268</t>
+          <t>263069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270943</t>
+          <t>271059</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>441983</t>
+          <t>442317</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>454041</t>
+          <t>454121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>711023</t>
+          <t>710776</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>724775</t>
+          <t>724675</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -7810,97 +7810,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,62 +7958,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3585</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104836</t>
+          <t>104986</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70431</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172726</t>
+          <t>173100</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>15433</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32932</t>
+          <t>32622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>20134</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43840</t>
+          <t>42339</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>628209</t>
+          <t>628752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>639516</t>
+          <t>639651</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>985268</t>
+          <t>985801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1012958</t>
+          <t>1013157</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1619143</t>
+          <t>1620770</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1645375</t>
+          <t>1647680</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5414-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1964</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>3524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14971</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23418</t>
+          <t>24347</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>356639</t>
+          <t>356831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>368675</t>
+          <t>368557</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>567851</t>
+          <t>568398</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>582220</t>
+          <t>582299</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>931153</t>
+          <t>930740</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>948621</t>
+          <t>948661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,77 +1322,77 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5650</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83871</t>
+          <t>83918</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54942</t>
+          <t>55259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141898</t>
+          <t>141236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149471</t>
+          <t>149481</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>484991</t>
+          <t>486132</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>496990</t>
+          <t>497134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>655807</t>
+          <t>654809</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>669677</t>
+          <t>669963</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1145012</t>
+          <t>1145656</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1164796</t>
+          <t>1164511</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18210</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19964</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29369</t>
+          <t>29536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43075</t>
+          <t>43601</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>387505</t>
+          <t>387789</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>405877</t>
+          <t>406006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>592960</t>
+          <t>594119</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>615749</t>
+          <t>615722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>990761</t>
+          <t>988306</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1018280</t>
+          <t>1017123</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>948</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>10143</t>
+          <t>10082</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108609</t>
+          <t>109107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117657</t>
+          <t>117620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73950</t>
+          <t>73758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82118</t>
+          <t>82086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>186664</t>
+          <t>186456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198594</t>
+          <t>198518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20454</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10939</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32148</t>
+          <t>31324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51686</t>
+          <t>49445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>528178</t>
+          <t>527851</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>547452</t>
+          <t>547199</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>694725</t>
+          <t>692702</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>718013</t>
+          <t>717976</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1229937</t>
+          <t>1229679</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1259874</t>
+          <t>1260266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14967</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>10083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30332</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>16992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39270</t>
+          <t>38928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>338934</t>
+          <t>338620</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>349680</t>
+          <t>349685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>512513</t>
+          <t>512638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>536816</t>
+          <t>537233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>859087</t>
+          <t>858112</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>884225</t>
+          <t>884404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187412</t>
+          <t>187927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>181092</t>
+          <t>181911</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>372799</t>
+          <t>372855</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>379700</t>
+          <t>379703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>67197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5299</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20050</t>
+          <t>20744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15712</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13013</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34111</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>19725</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42314</t>
+          <t>42878</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>571686</t>
+          <t>572127</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>583523</t>
+          <t>583397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>732058</t>
+          <t>731143</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>756715</t>
+          <t>756311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1310710</t>
+          <t>1308690</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1336587</t>
+          <t>1336260</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,9%</t>
         </is>
       </c>
     </row>
@@ -6893,67 +6893,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7258</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12582</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6711</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4019</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11295</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,27 +7041,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18378</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26154</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30626</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>262923</t>
+          <t>283790</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>258665</t>
+          <t>279368</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265695</t>
+          <t>286845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>475644</t>
+          <t>511590</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>466979</t>
+          <t>502763</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>481848</t>
+          <t>518577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>738567</t>
+          <t>795379</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>729487</t>
+          <t>786657</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>745287</t>
+          <t>803535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>500733</t>
+          <t>538781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>769976</t>
+          <t>828876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>865</t>
+          <t>879</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9273</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11747</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>16064</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>268358</t>
+          <t>298993</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>263069</t>
+          <t>293160</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>271059</t>
+          <t>301649</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>449682</t>
+          <t>271115</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>442317</t>
+          <t>266644</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>454121</t>
+          <t>273930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>718040</t>
+          <t>570108</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>710776</t>
+          <t>563744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>724675</t>
+          <t>574737</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455739</t>
+          <t>277646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>728996</t>
+          <t>581471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -7998,12 +7998,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -8031,27 +8031,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>104211</t>
+          <t>117621</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101156</t>
+          <t>114584</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8101,27 +8101,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>175536</t>
+          <t>200476</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173100</t>
+          <t>197275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>6718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15721</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15433</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>18488</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32622</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>26948</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>635492</t>
+          <t>700404</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>628752</t>
+          <t>693981</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>639651</t>
+          <t>704850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>996652</t>
+          <t>865560</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>985801</t>
+          <t>856368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1013157</t>
+          <t>873882</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1632143</t>
+          <t>1565963</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1620770</t>
+          <t>1554042</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1647680</t>
+          <t>1575726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>647487</t>
+          <t>712801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1027797</t>
+          <t>899282</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1675283</t>
+          <t>1612083</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1675283</t>
+          <t>1612083</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1675283</t>
+          <t>1612083</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
